--- a/letter analysis.xlsx
+++ b/letter analysis.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="20225"/>
+  <workbookPr autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="45" windowWidth="17235" windowHeight="9270"/>
+    <workbookView xWindow="1440" yWindow="8220" windowWidth="18160" windowHeight="19200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="140001" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
+      <mx:ArchID Flags="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -115,7 +120,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +139,22 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -162,18 +183,52 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="18">
+    <cellStyle name="Followed Hyperlink" xfId="3" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="5" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="11" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="13" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="15" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="17" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="4" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="8" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="10" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="12" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="14" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="16" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -474,15 +529,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -493,7 +548,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -504,8 +559,22 @@
         <f>B2/SUM(B$2:B$27)</f>
         <v>1.6162028573016231E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>1.69</v>
+      </c>
+      <c r="G2">
+        <v>1.69</v>
+      </c>
+      <c r="H2">
+        <f>G2/1.69</f>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>H2*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -516,8 +585,22 @@
         <f t="shared" ref="C3:C27" si="0">B3/SUM(B$2:B$27)</f>
         <v>1.6552187273023205E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>1.69</v>
+      </c>
+      <c r="G3">
+        <v>1.69</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H27" si="1">G3/1.69</f>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I27" si="2">H3*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -528,8 +611,22 @@
         <f t="shared" si="0"/>
         <v>2.7973196491409219E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>1.69</v>
+      </c>
+      <c r="G4">
+        <v>1.69</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -540,8 +637,22 @@
         <f t="shared" si="0"/>
         <v>4.8454557743290551E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>1.69</v>
+      </c>
+      <c r="G5">
+        <v>1.69</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -552,8 +663,22 @@
         <f t="shared" si="0"/>
         <v>7.349959348616257E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>1.69</v>
+      </c>
+      <c r="G6">
+        <v>1.69</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -564,8 +689,22 @@
         <f t="shared" si="0"/>
         <v>8.9251758374322993E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>1.69</v>
+      </c>
+      <c r="G7">
+        <v>1.69</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -576,8 +715,22 @@
         <f t="shared" si="0"/>
         <v>9.2325736010741583E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>1.69</v>
+      </c>
+      <c r="G8">
+        <v>1.69</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -588,8 +741,22 @@
         <f t="shared" si="0"/>
         <v>1.1711460695057872E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>1.69</v>
+      </c>
+      <c r="G9">
+        <v>1.69</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -600,8 +767,22 @@
         <f t="shared" si="0"/>
         <v>1.62794702827153E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>1.69</v>
+      </c>
+      <c r="G10">
+        <v>1.69</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -612,8 +793,23 @@
         <f t="shared" si="0"/>
         <v>1.8289772836993665E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>1.8289772836993665E-2</v>
+      </c>
+      <c r="G11">
+        <f>F11*100</f>
+        <v>1.8289772836993665</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="1"/>
+        <v>1.0822350791120512</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="2"/>
+        <v>108.22350791120512</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -624,8 +820,23 @@
         <f t="shared" si="0"/>
         <v>2.4907889048324111E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>2.4907889048324111E-2</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12:G27" si="3">F12*100</f>
+        <v>2.490788904832411</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="1"/>
+        <v>1.4738395886582314</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="2"/>
+        <v>147.38395886582313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -636,8 +847,23 @@
         <f t="shared" si="0"/>
         <v>2.7565303305038289E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>2.7565303305038289E-2</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="3"/>
+        <v>2.7565303305038289</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="1"/>
+        <v>1.6310830358010822</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="2"/>
+        <v>163.10830358010821</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -648,8 +874,23 @@
         <f t="shared" si="0"/>
         <v>2.8955292936275263E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>2.8955292936275263E-2</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="3"/>
+        <v>2.8955292936275261</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="1"/>
+        <v>1.7133309429748675</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="2"/>
+        <v>171.33309429748675</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -660,8 +901,23 @@
         <f t="shared" si="0"/>
         <v>3.0113551945689911E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>3.0113551945689911E-2</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="3"/>
+        <v>3.0113551945689911</v>
+      </c>
+      <c r="H15" s="5">
+        <f t="shared" si="1"/>
+        <v>1.781866979034906</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="2"/>
+        <v>178.1866979034906</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -672,8 +928,23 @@
         <f t="shared" si="0"/>
         <v>3.2890378410588041E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <v>3.2890378410588041E-2</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="3"/>
+        <v>3.2890378410588039</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="1"/>
+        <v>1.9461762373129019</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="2"/>
+        <v>194.61762373129019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -684,8 +955,23 @@
         <f t="shared" si="0"/>
         <v>3.307442296907618E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>3.307442296907618E-2</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="3"/>
+        <v>3.307442296907618</v>
+      </c>
+      <c r="H17" s="5">
+        <f t="shared" si="1"/>
+        <v>1.9570664478743303</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="2"/>
+        <v>195.70664478743302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -696,8 +982,23 @@
         <f t="shared" si="0"/>
         <v>4.0394430740722201E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <v>4.0394430740722201E-2</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="3"/>
+        <v>4.0394430740722198</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="1"/>
+        <v>2.3902030024095975</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="2"/>
+        <v>239.02030024095976</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -708,8 +1009,23 @@
         <f t="shared" si="0"/>
         <v>5.2336439758511467E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>5.2336439758511467E-2</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="3"/>
+        <v>5.2336439758511464</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="1"/>
+        <v>3.0968307549415068</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="2"/>
+        <v>309.68307549415067</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -720,8 +1036,23 @@
         <f t="shared" si="0"/>
         <v>6.5800067706327944E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>6.5800067706327944E-2</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="3"/>
+        <v>6.580006770632794</v>
+      </c>
+      <c r="H20" s="5">
+        <f t="shared" si="1"/>
+        <v>3.8934951305519494</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="2"/>
+        <v>389.34951305519496</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -732,8 +1063,23 @@
         <f t="shared" si="0"/>
         <v>6.6755759471496548E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>6.6755759471496548E-2</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="3"/>
+        <v>6.675575947149655</v>
+      </c>
+      <c r="H21" s="5">
+        <f t="shared" si="1"/>
+        <v>3.950044939141808</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="2"/>
+        <v>395.00449391418078</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -751,8 +1097,23 @@
       <c r="E22" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>6.7464350726660724E-2</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="3"/>
+        <v>6.7464350726660722</v>
+      </c>
+      <c r="H22" s="5">
+        <f t="shared" si="1"/>
+        <v>3.991973415778741</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="2"/>
+        <v>399.19734157787411</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -763,8 +1124,23 @@
         <f t="shared" si="0"/>
         <v>6.9687861217003516E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>6.9687861217003516E-2</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="3"/>
+        <v>6.9687861217003517</v>
+      </c>
+      <c r="H23" s="5">
+        <f t="shared" si="1"/>
+        <v>4.1235420838463623</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="2"/>
+        <v>412.35420838463625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -775,8 +1151,23 @@
         <f t="shared" si="0"/>
         <v>7.7169055764713029E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>7.7169055764713029E-2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="3"/>
+        <v>7.7169055764713033</v>
+      </c>
+      <c r="H24" s="5">
+        <f t="shared" si="1"/>
+        <v>4.5662163174386414</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="2"/>
+        <v>456.62163174386416</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -787,8 +1178,23 @@
         <f t="shared" si="0"/>
         <v>9.1025207010718326E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>9.1025207010718326E-2</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="3"/>
+        <v>9.1025207010718319</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" si="1"/>
+        <v>5.386106923711143</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="2"/>
+        <v>538.61069237111428</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -799,8 +1205,23 @@
         <f t="shared" si="0"/>
         <v>9.6391662584450644E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>9.6391662584450644E-2</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="3"/>
+        <v>9.6391662584450639</v>
+      </c>
+      <c r="H26" s="5">
+        <f t="shared" si="1"/>
+        <v>5.7036486736361329</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="2"/>
+        <v>570.36486736361326</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -810,6 +1231,27 @@
       <c r="C27" s="3">
         <f t="shared" si="0"/>
         <v>0.11276571679444036</v>
+      </c>
+      <c r="F27">
+        <v>0.11276571679444036</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="3"/>
+        <v>11.276571679444036</v>
+      </c>
+      <c r="H27" s="5">
+        <f t="shared" si="1"/>
+        <v>6.6725276209728026</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="2"/>
+        <v>667.25276209728031</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="B28">
+        <f>SUM(B2:B27)</f>
+        <v>2537429</v>
       </c>
     </row>
   </sheetData>
@@ -818,24 +1260,39 @@
     <sortCondition ref="B1:B26"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
 </worksheet>
 </file>